--- a/Familias.xlsx
+++ b/Familias.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +27,11 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -67,7 +72,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,7 +479,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Santana%20&amp;Familia2=Soto&amp;Cantidad=2</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Santana&amp;Familia2=Soto&amp;Cantidad=2</t>
         </is>
       </c>
     </row>
@@ -494,7 +499,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Portes&amp;Familia2=Guzm%C3%A1n&amp;Cantidad=4</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Portes&amp;Familia2=Guzm%C3%A1n&amp;Cantidad=4</t>
         </is>
       </c>
     </row>
@@ -514,7 +519,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=German&amp;Familia2=Soto&amp;Cantidad=3</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=German&amp;Familia2=Soto&amp;Cantidad=3</t>
         </is>
       </c>
     </row>
@@ -534,7 +539,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Berroa&amp;Familia2=Sim%C3%B3&amp;Cantidad=2</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Berroa&amp;Familia2=Sim%C3%B3&amp;Cantidad=2</t>
         </is>
       </c>
     </row>
@@ -554,7 +559,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=V%C3%A1squez&amp;Familia2=Mercedes&amp;Cantidad=2</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=V%C3%A1squez&amp;Familia2=Mercedes&amp;Cantidad=2</t>
         </is>
       </c>
     </row>
@@ -574,7 +579,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Mej%C3%ADa&amp;Familia2=Ram%C3%ADrez&amp;Cantidad=2</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Mej%C3%ADa&amp;Familia2=Ram%C3%ADrez&amp;Cantidad=2</t>
         </is>
       </c>
     </row>
@@ -594,7 +599,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Batista%20&amp;Familia2=Noyola&amp;Cantidad=2</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Batista&amp;Familia2=Noyola&amp;Cantidad=2</t>
         </is>
       </c>
     </row>
@@ -610,7 +615,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Doce&amp;Familia2=nan&amp;Cantidad=2</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Doce&amp;Familia2=&amp;Cantidad=2</t>
         </is>
       </c>
     </row>
@@ -630,7 +635,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Noel&amp;Familia2=Reyes&amp;Cantidad=3</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Noel&amp;Familia2=Reyes&amp;Cantidad=3</t>
         </is>
       </c>
     </row>
@@ -646,7 +651,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Joseph&amp;Familia2=nan&amp;Cantidad=3</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Joseph&amp;Familia2=&amp;Cantidad=3</t>
         </is>
       </c>
     </row>
@@ -666,7 +671,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Nuel&amp;Familia2=Jim%C3%A9nez&amp;Cantidad=2</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Nuel&amp;Familia2=Jim%C3%A9nez&amp;Cantidad=2</t>
         </is>
       </c>
     </row>
@@ -686,7 +691,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Francis&amp;Familia2=Nouel&amp;Cantidad=2</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Francis&amp;Familia2=Nouel&amp;Cantidad=2</t>
         </is>
       </c>
     </row>
@@ -706,7 +711,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Joseph&amp;Familia2=Nouel&amp;Cantidad=2</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Joseph&amp;Familia2=Nouel&amp;Cantidad=2</t>
         </is>
       </c>
     </row>
@@ -726,7 +731,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Reyes&amp;Familia2=Nouel&amp;Cantidad=2</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Reyes&amp;Familia2=Nouel&amp;Cantidad=2</t>
         </is>
       </c>
     </row>
@@ -746,7 +751,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Taveras&amp;Familia2=Rosario&amp;Cantidad=3</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Taveras&amp;Familia2=Rosario&amp;Cantidad=3</t>
         </is>
       </c>
     </row>
@@ -766,7 +771,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Fulgencio&amp;Familia2=S%C3%A1nchez&amp;Cantidad=3</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Fulgencio&amp;Familia2=S%C3%A1nchez&amp;Cantidad=3</t>
         </is>
       </c>
     </row>
@@ -786,7 +791,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Familia1=Cueto&amp;Familia2=Cornelio&amp;Cantidad=2</t>
+          <t>https://dayanyrashell.netlify.app/?Familia1=Cueto&amp;Familia2=Cornelio&amp;Cantidad=2</t>
         </is>
       </c>
     </row>
